--- a/AAII_Financials/Yearly/HPE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HPE_YR_FIN.xlsx
@@ -1011,13 +1011,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1962000</v>
+        <v>1952000</v>
       </c>
       <c r="E14" s="3">
-        <v>-412000</v>
+        <v>-416000</v>
       </c>
       <c r="F14" s="3">
-        <v>395000</v>
+        <v>389000</v>
       </c>
       <c r="G14" s="3">
         <v>1393000</v>
@@ -1131,13 +1131,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>32542000</v>
+        <v>32532000</v>
       </c>
       <c r="E17" s="3">
-        <v>27632000</v>
+        <v>27628000</v>
       </c>
       <c r="F17" s="3">
-        <v>26690000</v>
+        <v>26684000</v>
       </c>
       <c r="G17" s="3">
         <v>26118000</v>
@@ -1182,13 +1182,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1754000</v>
+        <v>1764000</v>
       </c>
       <c r="E18" s="3">
-        <v>2495000</v>
+        <v>2499000</v>
       </c>
       <c r="F18" s="3">
-        <v>2445000</v>
+        <v>2451000</v>
       </c>
       <c r="G18" s="3">
         <v>2378000</v>
@@ -1254,13 +1254,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-115000</v>
+        <v>-95000</v>
       </c>
       <c r="E20" s="3">
-        <v>-131000</v>
+        <v>-123000</v>
       </c>
       <c r="F20" s="3">
-        <v>-379000</v>
+        <v>-367000</v>
       </c>
       <c r="G20" s="3">
         <v>-112000</v>
@@ -1305,13 +1305,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2380000</v>
+        <v>2370000</v>
       </c>
       <c r="E21" s="3">
-        <v>2893000</v>
+        <v>2889000</v>
       </c>
       <c r="F21" s="3">
-        <v>3112000</v>
+        <v>3106000</v>
       </c>
       <c r="G21" s="3">
         <v>2783000</v>
@@ -1866,13 +1866,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>115000</v>
+        <v>95000</v>
       </c>
       <c r="E32" s="3">
-        <v>131000</v>
+        <v>123000</v>
       </c>
       <c r="F32" s="3">
-        <v>379000</v>
+        <v>367000</v>
       </c>
       <c r="G32" s="3">
         <v>112000</v>
